--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -328,7 +328,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" val="0"/>
+              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>24500</v>
+        <v>26250</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>59500</v>
+        <v>57750</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1311,9 +1311,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45380</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>

--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
@@ -14,9 +14,9 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -107,12 +107,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,7 +328,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -613,9 +613,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12"/>
     <col min="2" max="2" width="16.5703125" style="12" customWidth="1"/>
@@ -623,14 +623,14 @@
     <col min="4" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
     </row>
-    <row r="5" spans="2:3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
     </row>
-    <row r="7" spans="2:3" ht="16.5">
+    <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>5</v>
       </c>
@@ -638,7 +638,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="16.5">
+    <row r="8" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>6</v>
       </c>
@@ -646,7 +646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="16.5">
+    <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>7</v>
       </c>
@@ -654,7 +654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="16.5">
+    <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>8</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="16.5">
+    <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>9</v>
       </c>
@@ -670,7 +670,7 @@
         <v>9863328343</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="16.5">
+    <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
         <v>10</v>
       </c>
@@ -678,7 +678,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="16.5">
+    <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>11</v>
       </c>
@@ -686,7 +686,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="16.5">
+    <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>12</v>
       </c>
@@ -694,47 +694,47 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="16.5">
+    <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="2:3" ht="16.5">
+    <row r="16" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="14"/>
     </row>
-    <row r="17" spans="2:3" ht="16.5">
+    <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="22"/>
     </row>
-    <row r="19" spans="2:3" ht="16.5">
+    <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
-    <row r="21" spans="2:3" ht="16.5">
+    <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="22"/>
     </row>
-    <row r="22" spans="2:3" ht="16.5">
+    <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
     </row>
-    <row r="23" spans="2:3" ht="16.5">
+    <row r="23" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B23" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="15"/>
     </row>
-    <row r="24" spans="2:3" ht="16.5">
+    <row r="24" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
     </row>
-    <row r="25" spans="2:3" ht="16.5">
+    <row r="25" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
         <v>17</v>
       </c>
@@ -742,17 +742,17 @@
         <v>45212</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="16.5">
+    <row r="26" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
     </row>
-    <row r="27" spans="2:3" ht="16.5">
+    <row r="27" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="15"/>
     </row>
-    <row r="28" spans="2:3" ht="16.5">
+    <row r="28" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
     </row>
@@ -768,9 +768,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P32"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.140625" style="2" customWidth="1"/>
@@ -790,7 +790,7 @@
     <col min="17" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,11 +822,11 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>26250</v>
+        <v>33250</v>
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,11 +855,11 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>57750</v>
+        <v>50750</v>
       </c>
       <c r="P2" s="6"/>
     </row>
-    <row r="3" spans="1:16" ht="16.5" customHeight="1">
+    <row r="3" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -891,7 +891,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="16.5" customHeight="1">
+    <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -923,7 +923,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="16.5" customHeight="1">
+    <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -955,7 +955,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" ht="16.5" customHeight="1">
+    <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -987,7 +987,7 @@
       <c r="O6" s="4"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1019,7 +1019,7 @@
       <c r="O7" s="4"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="16.5" customHeight="1">
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1051,7 +1051,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" ht="16.5" customHeight="1">
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1083,7 +1083,7 @@
       <c r="O9" s="4"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" ht="16.5" customHeight="1">
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1115,7 +1115,7 @@
       <c r="O10" s="4"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" ht="16.5" customHeight="1">
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1147,7 +1147,7 @@
       <c r="O11" s="4"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" ht="16.5" customHeight="1">
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1179,7 +1179,7 @@
       <c r="O12" s="4"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" ht="16.5" customHeight="1">
+    <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1211,7 +1211,7 @@
       <c r="O13" s="4"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" ht="16.5" customHeight="1">
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1243,7 +1243,7 @@
       <c r="O14" s="4"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" ht="16.5" customHeight="1">
+    <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1275,7 +1275,7 @@
       <c r="O15" s="4"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" ht="16.5" customHeight="1">
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1307,7 +1307,7 @@
       <c r="O16" s="4"/>
       <c r="P16" s="1"/>
     </row>
-    <row r="17" spans="1:16" ht="16.5" customHeight="1">
+    <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1339,13 +1339,19 @@
       <c r="O17" s="4"/>
       <c r="P17" s="1"/>
     </row>
-    <row r="18" spans="1:16" ht="16.5" customHeight="1">
+    <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45387</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1365,13 +1371,19 @@
       <c r="O18" s="4"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="1:16" ht="16.5" customHeight="1">
+    <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45396</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1391,13 +1403,19 @@
       <c r="O19" s="4"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" ht="16.5" customHeight="1">
+    <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45403</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1417,13 +1435,19 @@
       <c r="O20" s="4"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" ht="16.5" customHeight="1">
+    <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45409</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1443,7 +1467,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="1"/>
     </row>
-    <row r="22" spans="1:16" ht="16.5" customHeight="1">
+    <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1469,7 +1493,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="1"/>
     </row>
-    <row r="23" spans="1:16" ht="16.5" customHeight="1">
+    <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1495,7 +1519,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="1:16" ht="16.5" customHeight="1">
+    <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1521,7 +1545,7 @@
       <c r="O24" s="4"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:16" ht="16.5" customHeight="1">
+    <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1547,7 +1571,7 @@
       <c r="O25" s="4"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="1:16" ht="16.5" customHeight="1">
+    <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1573,7 +1597,7 @@
       <c r="O26" s="4"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:16" ht="16.5" customHeight="1">
+    <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1599,7 +1623,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:16" ht="16.5" customHeight="1">
+    <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1625,7 +1649,7 @@
       <c r="O28" s="4"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:16" ht="16.5" customHeight="1">
+    <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1651,7 +1675,7 @@
       <c r="O29" s="4"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:16" ht="16.5" customHeight="1">
+    <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1677,7 +1701,7 @@
       <c r="O30" s="4"/>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" ht="16.5" customHeight="1">
+    <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1703,7 +1727,7 @@
       <c r="O31" s="4"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" ht="16.5" customHeight="1">
+    <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1741,9 +1765,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>33250</v>
+        <v>35000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>50750</v>
+        <v>49000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1471,9 +1471,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45416</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>

--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>35000</v>
+        <v>38500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>49000</v>
+        <v>45500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1503,9 +1503,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45425</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1529,9 +1535,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45431</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>

--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>38500</v>
+        <v>42000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>45500</v>
+        <v>42000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1567,9 +1567,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45437</v>
+      </c>
+      <c r="C25" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1593,9 +1599,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45444</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>

--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>42000</v>
+        <v>50750</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>42000</v>
+        <v>33250</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1631,9 +1631,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45451</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1657,9 +1663,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45458</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1683,9 +1695,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45465</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1709,9 +1727,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45474</v>
+      </c>
+      <c r="C30" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1735,9 +1759,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45478</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>

--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>50750</v>
+        <v>56000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>33250</v>
+        <v>28000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -875,9 +875,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45495</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -907,9 +913,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45500</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -1791,9 +1803,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45487</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>56000</v>
+        <v>70000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>28000</v>
+        <v>14000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -951,9 +951,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45506</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -983,9 +989,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45514</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1015,9 +1027,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45522</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1047,9 +1065,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45527</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1079,9 +1103,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45536</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1111,9 +1141,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45544</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1143,9 +1179,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45553</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1175,9 +1217,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45558</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>

--- a/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
+++ b/LoanOfficer-A/2023/11 Moirangthem Naobi.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>70000</v>
+        <v>75250</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>14000</v>
+        <v>8750</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1255,9 +1255,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45565</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1287,9 +1293,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45572</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1319,9 +1331,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45576</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
